--- a/consent_forms/026_ai_medical_scribe_consent_form--consent_forms.xlsx
+++ b/consent_forms/026_ai_medical_scribe_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -950,12 +950,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -983,12 +983,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'i_consent_to_audio_recording',_'value':_true}</t>
+          <t>i_consent_to_audio_recording</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'I Consent to Audio Recording', 'value': True}</t>
+          <t>I Consent to Audio Recording</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'i_do_not_consent_(opt-out)',_'value':_false}</t>
+          <t>i_do_not_consent_(opt-out)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'I Do Not Consent (Opt-Out)', 'value': False}</t>
+          <t>I Do Not Consent (Opt-Out)</t>
         </is>
       </c>
     </row>
@@ -1017,97 +1017,165 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'i_understand',_'value':_'understood'}</t>
+          <t>i_understand</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'I understand', 'value': 'understood'}</t>
+          <t>I understand</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>data_privacy_hipaa_ack_choices</t>
+          <t>human_review_ack_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'i_understand_the_privacy_terms',_'value':_'understood'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'I understand the privacy terms', 'value': 'understood'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>right_to_withdraw_consent_choices</t>
+          <t>data_privacy_hipaa_ack_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'i_understand',_'value':_'understood'}</t>
+          <t>i_understand_the_privacy_terms</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'I understand', 'value': 'understood'}</t>
+          <t>I understand the privacy terms</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>summary_request_choices</t>
+          <t>data_privacy_hipaa_ack_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_please_email_it_to_me',_'value':_true}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, please email it to me', 'value': True}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>summary_request_choices</t>
+          <t>right_to_withdraw_consent_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'no,_thank_you',_'value':_false}</t>
+          <t>i_understand</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'No, thank you', 'value': False}</t>
+          <t>I understand</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>right_to_withdraw_consent_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>summary_request_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>yes,_please_email_it_to_me</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Yes, please email it to me</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>summary_request_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>no,_thank_you</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>No, thank you</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>signature_selection_choices</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'label':_'i_agree_and_provide_my_digital_signature',_'value':_'signed'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'label': 'I agree and provide my digital signature', 'value': 'signed'}</t>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>i_agree_and_provide_my_digital_signature</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>I agree and provide my digital signature</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>signature_selection_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
